--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -2,39 +2,375 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="7305" windowHeight="6517" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,15 +378,305 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -403,7 +1029,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -413,8 +1038,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -514,7 +1139,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F4" t="n">
         <v>5</v>
@@ -538,11 +1163,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DogKnight</t>
+          <t>Mafe</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -550,6 +1175,90 @@
       <c r="G5" t="inlineStr">
         <is>
           <t>A0,ES002,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Enemy003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>重装步兵</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DogKnight</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>140</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Enemy004</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>冰焰法师</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wangg</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>65</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Enemy005</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>急袭兵</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Remy</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -1,184 +1,293 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="7305" windowHeight="6517" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="21000" windowHeight="11655"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlternativePath</t>
+  </si>
+  <si>
+    <t>Hp</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>IntentionSet</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>(list#sep=;),EnemyIntentions</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>Enemy001</t>
+  </si>
+  <si>
+    <t>小兵</t>
+  </si>
+  <si>
+    <t>DogKnight</t>
+  </si>
+  <si>
+    <t>A0,ES001,3</t>
+  </si>
+  <si>
+    <t>Enemy002</t>
+  </si>
+  <si>
+    <t>小兵2</t>
+  </si>
+  <si>
+    <t>Mafe</t>
+  </si>
+  <si>
+    <t>A0,ES002,6</t>
+  </si>
+  <si>
+    <t>Enemy003</t>
+  </si>
+  <si>
+    <t>重装步兵</t>
+  </si>
+  <si>
+    <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
+  </si>
+  <si>
+    <t>Enemy004</t>
+  </si>
+  <si>
+    <t>冰焰法师</t>
+  </si>
+  <si>
+    <t>Wangg</t>
+  </si>
+  <si>
+    <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
+  </si>
+  <si>
+    <t>Enemy005</t>
+  </si>
+  <si>
+    <t>急袭兵</t>
+  </si>
+  <si>
+    <t>Remy</t>
+  </si>
+  <si>
+    <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="21">
-    <font>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -478,154 +587,154 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -679,74 +788,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1033,236 +1079,164 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>##var</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>AlternativePath</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Hp</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>IntentionSet</t>
-        </is>
+    <row r="1" spans="1:7">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>##type</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>(list#sep=;),EnemyIntentions</t>
-        </is>
+    <row r="2" spans="1:7">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>##group</t>
-        </is>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Enemy001</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>小兵</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DogKnight</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>100</v>
-      </c>
-      <c r="F4" t="n">
+    <row r="4" spans="1:7">
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
         <v>5</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>A0,ES001,3</t>
-        </is>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Enemy002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>小兵2</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mafe</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>70</v>
-      </c>
-      <c r="F5" t="n">
+    <row r="5" spans="1:7">
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
         <v>5</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>A0,ES002,6</t>
-        </is>
+      <c r="G5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Enemy003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>重装步兵</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DogKnight</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>140</v>
-      </c>
-      <c r="F6" t="n">
+    <row r="6" spans="1:7">
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
-        </is>
+      <c r="G6" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Enemy004</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>冰焰法师</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Wangg</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>65</v>
-      </c>
-      <c r="F7" t="n">
+    <row r="7" spans="1:7">
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
         <v>5</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
-        </is>
+      <c r="G7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Enemy005</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>急袭兵</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Remy</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>55</v>
-      </c>
-      <c r="F8" t="n">
+    <row r="8" spans="1:7">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
         <v>7</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
-        </is>
+      <c r="G8" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -120,6 +120,18 @@
   </si>
   <si>
     <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
+  </si>
+  <si>
+    <t>Enemy006</t>
+  </si>
+  <si>
+    <t>Boss1号</t>
+  </si>
+  <si>
+    <t>Boss1</t>
+  </si>
+  <si>
+    <t>A0,ES011,3;S0,ES013,5;A1,ES012,7;S1,ES014,14</t>
   </si>
 </sst>
 </file>
@@ -1081,8 +1093,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
@@ -1146,7 +1158,7 @@
         <v>14</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -1166,7 +1178,7 @@
         <v>18</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F5">
         <v>5</v>
@@ -1186,7 +1198,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -1233,6 +1245,26 @@
       </c>
       <c r="G8" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10">
+        <v>300</v>
+      </c>
+      <c r="F10">
+        <v>2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -1,305 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="11655"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="28800" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>AlternativePath</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>IntentionSet</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>(list#sep=;),EnemyIntentions</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>Enemy001</t>
-  </si>
-  <si>
-    <t>小兵</t>
-  </si>
-  <si>
-    <t>DogKnight</t>
-  </si>
-  <si>
-    <t>A0,ES001,3</t>
-  </si>
-  <si>
-    <t>Enemy002</t>
-  </si>
-  <si>
-    <t>小兵2</t>
-  </si>
-  <si>
-    <t>Mafe</t>
-  </si>
-  <si>
-    <t>A0,ES002,6</t>
-  </si>
-  <si>
-    <t>Enemy003</t>
-  </si>
-  <si>
-    <t>重装步兵</t>
-  </si>
-  <si>
-    <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
-  </si>
-  <si>
-    <t>Enemy004</t>
-  </si>
-  <si>
-    <t>冰焰法师</t>
-  </si>
-  <si>
-    <t>Wangg</t>
-  </si>
-  <si>
-    <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
-  </si>
-  <si>
-    <t>Enemy005</t>
-  </si>
-  <si>
-    <t>急袭兵</t>
-  </si>
-  <si>
-    <t>Remy</t>
-  </si>
-  <si>
-    <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
-  </si>
-  <si>
-    <t>Enemy006</t>
-  </si>
-  <si>
-    <t>Boss1号</t>
-  </si>
-  <si>
-    <t>Boss1</t>
-  </si>
-  <si>
-    <t>A0,ES011,3;S0,ES013,5;A1,ES012,7;S1,ES014,14</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <b val="1"/>
+      <color theme="3"/>
       <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <b val="1"/>
       <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -600,153 +472,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -800,11 +672,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1091,184 +1026,265 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>AlternativePath</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Hp</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IntentionSet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),EnemyIntentions</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enemy001</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>狗骑士</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DogKnight</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>50</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A0,ES001,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Enemy002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>马匪</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mafe</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>A0,ES002,6</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Enemy003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>重装步兵</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DogKnight</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Enemy004</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>汪汪</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Wangg</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Enemy005</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>雷米</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Remy</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Enemy006</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Boss1号</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Boss1</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>300</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4">
-        <v>30</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-      <c r="G4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5">
-        <v>40</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6">
-        <v>100</v>
-      </c>
-      <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7">
-        <v>10</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10">
-        <v>300</v>
-      </c>
-      <c r="F10">
-        <v>2</v>
-      </c>
-      <c r="G10" t="s">
-        <v>34</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A0,ES011,3;S0,ES013,5;A1,ES012,7;S1,ES014,14</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1070,6 +1070,16 @@
           <t>IntentionSet</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IsElite</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>StartRow</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1107,6 +1117,16 @@
           <t>(list#sep=;),EnemyIntentions</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>TargetZoneEnum</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1142,6 +1162,14 @@
           <t>A0,ES001,3</t>
         </is>
       </c>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
@@ -1170,6 +1198,14 @@
           <t>A0,ES002,6</t>
         </is>
       </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
@@ -1198,6 +1234,14 @@
           <t>A0,ES005,3;A1,ES003,8;A2,ES001,3</t>
         </is>
       </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -1226,6 +1270,14 @@
           <t>A0,ES007,4;A1,ES004,5;S0,ES008,10</t>
         </is>
       </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -1252,6 +1304,14 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>A0,ES006,2;S0,ES009,3;S1,ES010,3</t>
+        </is>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Front</t>
         </is>
       </c>
     </row>
@@ -1281,6 +1341,194 @@
       <c r="G10" t="inlineStr">
         <is>
           <t>A0,ES011,3;S0,ES013,5;A1,ES012,7;S1,ES014,14</t>
+        </is>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Enemy101</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>掠林狂犬</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Remy</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>A0,ES101,1;A1,ES102,1</t>
+        </is>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Enemy102</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>影猎收税人</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Wangg</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>45</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A0,ES103,2;A1,ES104,2</t>
+        </is>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Enemy103</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>蚀骨炮台</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Mafe</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A0,ES105,5;A1,ES106,4</t>
+        </is>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Enemy104</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>锈牙掠犬</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DogKnight</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>A0,ES101,1</t>
+        </is>
+      </c>
+      <c r="H14" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Enemy105</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>断律者</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Boss1</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>180</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>A0,ES107,2;A1,ES108,3;A2,ES109,2;S0,ES110,7</t>
+        </is>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Front</t>
         </is>
       </c>
     </row>

--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -1031,7 +1031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,258 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>EnemyM01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>灰袍信徒</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Grey</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>A0,ESM01,1;A1,ESM02,2</t>
+        </is>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EnemyM02</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>蒙眼侍僧</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Tusk</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>54</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>A0,ESM03,2;A1,ESM04,3</t>
+        </is>
+      </c>
+      <c r="H17" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>EnemyM03</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>戒律执事</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Banner</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>72</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>A0,ESM05,3;A1,ESM06,5</t>
+        </is>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>EnemyM04</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>缄默使徒</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mafe</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>150</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>A0,ESM07,2;A1,ESM08,2;A2,ESM09,5</t>
+        </is>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>EnemyW01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>指裔</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Tusk</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>36</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>A0,ESW01,1;A1,ESW02,1</t>
+        </is>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EnemyW02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>血肉猎手</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Wangg</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>54</v>
+      </c>
+      <c r="F21" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A0,ESW03,2;A1,ESW04,3</t>
+        </is>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>EnemyW03</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>多臂殉道者</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mafe</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>72</v>
+      </c>
+      <c r="F22" t="n">
+        <v>4</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>A0,ESW05,3;A1,ESW06,5</t>
+        </is>
+      </c>
+      <c r="H22" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Front</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DataTables/Datas/Enemy/#EnemyInfo.xlsx
+++ b/DataTables/Datas/Enemy/#EnemyInfo.xlsx
@@ -1545,7 +1545,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Grey</t>
+          <t>AshrobeDevotee</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tusk</t>
+          <t>VeiledAcolyte</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Banner</t>
+          <t>TheDisciplinarian</t>
         </is>
       </c>
       <c r="E18" t="n">
